--- a/Claude_ai/Skills/Examples/Level3_Expense_Auditor/templates/expense-report-template.xlsx
+++ b/Claude_ai/Skills/Examples/Level3_Expense_Auditor/templates/expense-report-template.xlsx
@@ -94,7 +94,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -138,11 +138,55 @@
         <color rgb="001B365D"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9DDE3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9DDE3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9DDE3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9DDE3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9DDE3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9DDE3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9DDE3"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001B365D"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -194,6 +238,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -268,6 +314,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7239000" cy="533400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -841,10 +917,10 @@
           <t>報銷申請總計 Total (NT$)：</t>
         </is>
       </c>
-      <c r="B19" s="15" t="n"/>
-      <c r="C19" s="15" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="15" t="n"/>
+      <c r="B19" s="19" t="n"/>
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="19" t="n"/>
       <c r="F19" s="16">
         <f>SUM(F9:F18)</f>
         <v/>
@@ -859,27 +935,35 @@
           <t>申請人 (Applicant)</t>
         </is>
       </c>
+      <c r="B21" s="20" t="n"/>
       <c r="C21" s="3" t="inlineStr">
         <is>
           <t>部門主管核准 (Manager)</t>
         </is>
       </c>
+      <c r="D21" s="20" t="n"/>
       <c r="E21" s="3" t="inlineStr">
         <is>
           <t>財務複核 (Finance)</t>
         </is>
       </c>
+      <c r="F21" s="20" t="n"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
           <t>出納/發票放款 (Cashier)</t>
         </is>
       </c>
+      <c r="H21" s="20" t="n"/>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="17" t="n"/>
+      <c r="B22" s="20" t="n"/>
       <c r="C22" s="17" t="n"/>
+      <c r="D22" s="20" t="n"/>
       <c r="E22" s="17" t="n"/>
+      <c r="F22" s="20" t="n"/>
       <c r="G22" s="17" t="n"/>
+      <c r="H22" s="20" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1"/>
     <row r="24" ht="10" customHeight="1"/>
@@ -906,5 +990,6 @@
     <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>